--- a/data/trans_orig/P35-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P35-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2007 (tasa de respuesta: 95,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33712</t>
+          <t>32774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35695</t>
+          <t>36471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63766</t>
+          <t>59974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>436759</t>
+          <t>437697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>456353</t>
+          <t>455790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>408042</t>
+          <t>407266</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427909</t>
+          <t>427706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>850442</t>
+          <t>854234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879861</t>
+          <t>880531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18430</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39741</t>
+          <t>39503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45721</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75865</t>
+          <t>76721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70805</t>
+          <t>71415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106821</t>
+          <t>107676</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>662178</t>
+          <t>662416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>683489</t>
+          <t>683937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512329</t>
+          <t>511473</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>542473</t>
+          <t>541832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1183292</t>
+          <t>1182437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1219308</t>
+          <t>1218698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43562</t>
+          <t>44185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73297</t>
+          <t>73474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67296</t>
+          <t>65576</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>101752</t>
+          <t>103381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118968</t>
+          <t>120600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164774</t>
+          <t>167741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539416</t>
+          <t>539239</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>569151</t>
+          <t>568528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>550275</t>
+          <t>548646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>584731</t>
+          <t>586451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1099966</t>
+          <t>1096999</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1145772</t>
+          <t>1144140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54878</t>
+          <t>54747</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85091</t>
+          <t>86047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77182</t>
+          <t>78554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112739</t>
+          <t>112374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142752</t>
+          <t>142236</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189067</t>
+          <t>189275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>402971</t>
+          <t>402015</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>433184</t>
+          <t>433315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>376697</t>
+          <t>377062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412254</t>
+          <t>410882</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>788431</t>
+          <t>788223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>834746</t>
+          <t>835262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115782</t>
+          <t>115797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150731</t>
+          <t>152033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110785</t>
+          <t>109656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146070</t>
+          <t>144508</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237659</t>
+          <t>236839</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>288682</t>
+          <t>287976</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>216592</t>
+          <t>215290</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>251541</t>
+          <t>251526</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>246861</t>
+          <t>248423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>282146</t>
+          <t>283275</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>471572</t>
+          <t>472278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>522595</t>
+          <t>523415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111086</t>
+          <t>111920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>144650</t>
+          <t>146076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>134025</t>
+          <t>135279</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>168551</t>
+          <t>167657</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>254375</t>
+          <t>255134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>301235</t>
+          <t>302338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>138727</t>
+          <t>137301</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>172291</t>
+          <t>171457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>154515</t>
+          <t>155409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>189041</t>
+          <t>187787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>305208</t>
+          <t>304105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>352068</t>
+          <t>351309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,93%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92787</t>
+          <t>94415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121291</t>
+          <t>121760</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130014</t>
+          <t>130313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169128</t>
+          <t>169313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>235633</t>
+          <t>238709</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>282818</t>
+          <t>284903</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82066</t>
+          <t>81597</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110570</t>
+          <t>108942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149515</t>
+          <t>149330</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188629</t>
+          <t>188330</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>239182</t>
+          <t>237097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>286367</t>
+          <t>283291</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>504055</t>
+          <t>510422</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>589433</t>
+          <t>590682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>643049</t>
+          <t>645355</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>737446</t>
+          <t>734471</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1182969</t>
+          <t>1178787</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1304283</t>
+          <t>1297968</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2537790</t>
+          <t>2536541</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2623168</t>
+          <t>2616801</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2470587</t>
+          <t>2473562</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2564984</t>
+          <t>2562678</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5030973</t>
+          <t>5037288</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5152287</t>
+          <t>5156469</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,39%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2012 (tasa de respuesta: 97,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15379</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>33276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44696</t>
+          <t>44160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73143</t>
+          <t>71983</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64499</t>
+          <t>65236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102232</t>
+          <t>98828</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404522</t>
+          <t>406759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424656</t>
+          <t>425969</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>344211</t>
+          <t>345371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>372658</t>
+          <t>373194</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>755156</t>
+          <t>758560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>792889</t>
+          <t>792152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71256</t>
+          <t>72386</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107563</t>
+          <t>109004</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103473</t>
+          <t>104410</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144227</t>
+          <t>144389</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>186965</t>
+          <t>186355</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>239514</t>
+          <t>242020</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>559077</t>
+          <t>557636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>595384</t>
+          <t>594254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447868</t>
+          <t>447706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488622</t>
+          <t>487685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1019221</t>
+          <t>1016715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1071770</t>
+          <t>1072380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94004</t>
+          <t>93020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131904</t>
+          <t>132348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164604</t>
+          <t>167985</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>215168</t>
+          <t>212894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268491</t>
+          <t>269479</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>334038</t>
+          <t>331166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522601</t>
+          <t>522157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560501</t>
+          <t>561485</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>477326</t>
+          <t>479600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527890</t>
+          <t>524509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1012961</t>
+          <t>1015833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1078508</t>
+          <t>1077520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128599</t>
+          <t>127237</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172015</t>
+          <t>172767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183210</t>
+          <t>183074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232347</t>
+          <t>234078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>324808</t>
+          <t>320048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>391350</t>
+          <t>386557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>427254</t>
+          <t>426502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>470670</t>
+          <t>472032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366116</t>
+          <t>364385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>415253</t>
+          <t>415389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>806382</t>
+          <t>811175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>872924</t>
+          <t>877684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175489</t>
+          <t>176492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>220991</t>
+          <t>217024</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198760</t>
+          <t>199643</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>243705</t>
+          <t>244146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>387476</t>
+          <t>388408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>449849</t>
+          <t>446892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201013</t>
+          <t>204980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246515</t>
+          <t>245512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186459</t>
+          <t>186018</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>231404</t>
+          <t>230521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>402318</t>
+          <t>405275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>464691</t>
+          <t>463759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142601</t>
+          <t>142974</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>180743</t>
+          <t>178761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>177848</t>
+          <t>176902</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>214730</t>
+          <t>212955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>326352</t>
+          <t>331420</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>381097</t>
+          <t>383202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,21%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123029</t>
+          <t>125011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161171</t>
+          <t>160798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128642</t>
+          <t>130417</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>165524</t>
+          <t>166470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>266047</t>
+          <t>263942</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>320792</t>
+          <t>315724</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>48,79%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118192</t>
+          <t>118648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>154022</t>
+          <t>150672</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>174303</t>
+          <t>173452</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213672</t>
+          <t>212978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>301087</t>
+          <t>303960</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>355726</t>
+          <t>354439</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>87286</t>
+          <t>90636</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123116</t>
+          <t>122660</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164502</t>
+          <t>165196</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>203871</t>
+          <t>204722</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>263756</t>
+          <t>265043</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>318395</t>
+          <t>315522</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>808315</t>
+          <t>808044</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>918082</t>
+          <t>923851</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1128156</t>
+          <t>1128096</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1243553</t>
+          <t>1245567</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1976645</t>
+          <t>1982308</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2138551</t>
+          <t>2128182</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2409452</t>
+          <t>2403683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2519219</t>
+          <t>2519490</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2208561</t>
+          <t>2206547</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2323958</t>
+          <t>2324018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4641097</t>
+          <t>4651466</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4803003</t>
+          <t>4797340</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2016 (tasa de respuesta: 98,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29710</t>
+          <t>29274</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52742</t>
+          <t>53058</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33482</t>
+          <t>33689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57447</t>
+          <t>57774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69402</t>
+          <t>68963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104045</t>
+          <t>104122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355620</t>
+          <t>355304</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>378652</t>
+          <t>379088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>332011</t>
+          <t>331684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>355976</t>
+          <t>355769</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>693775</t>
+          <t>693698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>728418</t>
+          <t>728857</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59200</t>
+          <t>58853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91235</t>
+          <t>92518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116843</t>
+          <t>116518</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155081</t>
+          <t>157299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>185541</t>
+          <t>186073</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>234395</t>
+          <t>236374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491475</t>
+          <t>490192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>523510</t>
+          <t>523857</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>403060</t>
+          <t>400842</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>441298</t>
+          <t>441623</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906456</t>
+          <t>904477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>955310</t>
+          <t>954778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108856</t>
+          <t>109022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152788</t>
+          <t>151834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155920</t>
+          <t>157660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202792</t>
+          <t>202703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>276362</t>
+          <t>282821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>339229</t>
+          <t>343880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505762</t>
+          <t>506716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549694</t>
+          <t>549528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>448142</t>
+          <t>448231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>495014</t>
+          <t>493274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>970254</t>
+          <t>965603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033121</t>
+          <t>1026662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177476</t>
+          <t>176519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227830</t>
+          <t>225541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>202353</t>
+          <t>201292</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>248736</t>
+          <t>252519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>389480</t>
+          <t>390572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>462373</t>
+          <t>461778</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>413041</t>
+          <t>415330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>463395</t>
+          <t>464352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>390806</t>
+          <t>387023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>437189</t>
+          <t>438250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>818039</t>
+          <t>818634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>890932</t>
+          <t>889840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>168642</t>
+          <t>170108</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>215783</t>
+          <t>214163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>209576</t>
+          <t>210423</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>256539</t>
+          <t>259269</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>392403</t>
+          <t>388954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>455024</t>
+          <t>454671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,2%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257082</t>
+          <t>258702</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>304223</t>
+          <t>302757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233850</t>
+          <t>231120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>280813</t>
+          <t>279966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>508230</t>
+          <t>508583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570851</t>
+          <t>574300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,62%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>157286</t>
+          <t>158834</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>194859</t>
+          <t>194411</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>195781</t>
+          <t>194951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>233437</t>
+          <t>231889</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367026</t>
+          <t>366067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>418553</t>
+          <t>418645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>131212</t>
+          <t>131660</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168785</t>
+          <t>167237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>135223</t>
+          <t>136771</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172879</t>
+          <t>173709</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>276178</t>
+          <t>276086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>327705</t>
+          <t>328664</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104683</t>
+          <t>103506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131989</t>
+          <t>131465</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165167</t>
+          <t>165707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209035</t>
+          <t>209071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>277926</t>
+          <t>276737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>330130</t>
+          <t>332782</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,28%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118102</t>
+          <t>118626</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>145408</t>
+          <t>146585</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>189792</t>
+          <t>189756</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>233660</t>
+          <t>233120</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>318788</t>
+          <t>316136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>370992</t>
+          <t>372181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>874749</t>
+          <t>878132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>984567</t>
+          <t>981053</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1157730</t>
+          <t>1148481</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1281273</t>
+          <t>1268184</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2070915</t>
+          <t>2071546</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2231270</t>
+          <t>2225499</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2354953</t>
+          <t>2358467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2464771</t>
+          <t>2461388</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2214676</t>
+          <t>2227765</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2338219</t>
+          <t>2347468</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4604199</t>
+          <t>4609970</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4764554</t>
+          <t>4763923</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,69%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37938</t>
+          <t>39103</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87308</t>
+          <t>85365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66512</t>
+          <t>67065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108563</t>
+          <t>106732</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115806</t>
+          <t>114112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177698</t>
+          <t>177179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>312679</t>
+          <t>314622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362049</t>
+          <t>360884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>204637</t>
+          <t>206468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246688</t>
+          <t>246135</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>535489</t>
+          <t>536008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>597381</t>
+          <t>599075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81159</t>
+          <t>84280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126902</t>
+          <t>130946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66543</t>
+          <t>68249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133874</t>
+          <t>134268</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>164566</t>
+          <t>159719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246616</t>
+          <t>246246</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>296645</t>
+          <t>292601</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342388</t>
+          <t>339267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>377630</t>
+          <t>377236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444961</t>
+          <t>443255</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>688435</t>
+          <t>688805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>770485</t>
+          <t>775332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117026</t>
+          <t>116566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158439</t>
+          <t>158081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>155182</t>
+          <t>154871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>191524</t>
+          <t>190245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>285609</t>
+          <t>284331</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340272</t>
+          <t>337630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>377899</t>
+          <t>378257</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>419312</t>
+          <t>419772</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>349653</t>
+          <t>350932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>385995</t>
+          <t>386306</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>737243</t>
+          <t>739885</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>791906</t>
+          <t>793184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95596</t>
+          <t>93237</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>314067</t>
+          <t>313578</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>214904</t>
+          <t>220505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>278537</t>
+          <t>281043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273326</t>
+          <t>292745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>575281</t>
+          <t>573570</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>573719</t>
+          <t>574208</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>792190</t>
+          <t>794549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>433231</t>
+          <t>430725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>496864</t>
+          <t>491263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1024273</t>
+          <t>1025984</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1326228</t>
+          <t>1306809</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>223340</t>
+          <t>225386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>271196</t>
+          <t>269493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>224264</t>
+          <t>225565</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258977</t>
+          <t>258746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>462373</t>
+          <t>460538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>518117</t>
+          <t>517400</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>290038</t>
+          <t>291741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337894</t>
+          <t>335848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>286241</t>
+          <t>286472</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>320954</t>
+          <t>319653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>588335</t>
+          <t>589052</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>644079</t>
+          <t>645914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>164732</t>
+          <t>165421</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>197585</t>
+          <t>197170</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78699</t>
+          <t>75158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>294108</t>
+          <t>293742</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>205141</t>
+          <t>202107</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480898</t>
+          <t>480806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,26%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170580</t>
+          <t>170995</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203433</t>
+          <t>202744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>313718</t>
+          <t>314084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>529127</t>
+          <t>532668</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>495093</t>
+          <t>495185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>770850</t>
+          <t>773884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>132356</t>
+          <t>131169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159116</t>
+          <t>159121</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>195053</t>
+          <t>194426</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223156</t>
+          <t>223315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>333730</t>
+          <t>335508</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>373088</t>
+          <t>374950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123643</t>
+          <t>123638</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150403</t>
+          <t>151590</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202271</t>
+          <t>202112</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>230374</t>
+          <t>231001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>335098</t>
+          <t>333236</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>374456</t>
+          <t>372678</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>862249</t>
+          <t>843324</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1204823</t>
+          <t>1198696</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1043356</t>
+          <t>1005768</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1361965</t>
+          <t>1371118</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2032995</t>
+          <t>2048831</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2509442</t>
+          <t>2530350</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2254994</t>
+          <t>2261121</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2597568</t>
+          <t>2616493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2294154</t>
+          <t>2285001</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2612763</t>
+          <t>2650351</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4606494</t>
+          <t>4585586</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5082941</t>
+          <t>5067105</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P35-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32774</t>
+          <t>34381</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36471</t>
+          <t>34805</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33677</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59974</t>
+          <t>60258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437697</t>
+          <t>436090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455790</t>
+          <t>455920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>407266</t>
+          <t>408932</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427706</t>
+          <t>427735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>854234</t>
+          <t>853950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>880531</t>
+          <t>879826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39503</t>
+          <t>39185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>46241</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76721</t>
+          <t>76560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71415</t>
+          <t>71738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107676</t>
+          <t>106246</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>662416</t>
+          <t>662734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>683937</t>
+          <t>682847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>511473</t>
+          <t>511634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>541832</t>
+          <t>541953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1182437</t>
+          <t>1183867</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1218698</t>
+          <t>1218375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44185</t>
+          <t>44371</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73474</t>
+          <t>74899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65576</t>
+          <t>67511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103381</t>
+          <t>102399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120600</t>
+          <t>120006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167741</t>
+          <t>164312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539239</t>
+          <t>537814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>568528</t>
+          <t>568342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>548646</t>
+          <t>549628</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>586451</t>
+          <t>584516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1096999</t>
+          <t>1100428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1144140</t>
+          <t>1144734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54747</t>
+          <t>54822</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86047</t>
+          <t>86890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78554</t>
+          <t>78842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112374</t>
+          <t>113941</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142236</t>
+          <t>142103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189275</t>
+          <t>188632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,3%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>402015</t>
+          <t>401172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>433315</t>
+          <t>433240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>377062</t>
+          <t>375495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>410882</t>
+          <t>410594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>788223</t>
+          <t>788866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>835262</t>
+          <t>835395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115797</t>
+          <t>115931</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152033</t>
+          <t>152629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109656</t>
+          <t>110882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144508</t>
+          <t>148972</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236839</t>
+          <t>233448</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>287976</t>
+          <t>288484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>215290</t>
+          <t>214694</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>251526</t>
+          <t>251392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>248423</t>
+          <t>243959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>283275</t>
+          <t>282049</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>472278</t>
+          <t>471770</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>523415</t>
+          <t>526806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111920</t>
+          <t>110978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146076</t>
+          <t>145263</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135279</t>
+          <t>134018</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>167657</t>
+          <t>168650</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>255134</t>
+          <t>255530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>302338</t>
+          <t>302526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137301</t>
+          <t>138114</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171457</t>
+          <t>172399</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155409</t>
+          <t>154416</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187787</t>
+          <t>189048</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>304105</t>
+          <t>303917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>351309</t>
+          <t>350913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94415</t>
+          <t>94549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121760</t>
+          <t>122210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130313</t>
+          <t>132147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>171621</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>238709</t>
+          <t>234971</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>284903</t>
+          <t>281577</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81597</t>
+          <t>81147</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108942</t>
+          <t>108808</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149330</t>
+          <t>147022</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188330</t>
+          <t>186496</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>237097</t>
+          <t>240423</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283291</t>
+          <t>287029</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>510422</t>
+          <t>508961</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>590682</t>
+          <t>587680</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>645355</t>
+          <t>647402</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>734471</t>
+          <t>744599</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1178787</t>
+          <t>1179306</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1297968</t>
+          <t>1298809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2536541</t>
+          <t>2539543</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2616801</t>
+          <t>2618262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2473562</t>
+          <t>2463434</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2562678</t>
+          <t>2560631</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5037288</t>
+          <t>5036447</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5156469</t>
+          <t>5155950</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14066</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33276</t>
+          <t>33888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44160</t>
+          <t>44595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71983</t>
+          <t>72240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65236</t>
+          <t>65904</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98828</t>
+          <t>98969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406759</t>
+          <t>406147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425969</t>
+          <t>424414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>345371</t>
+          <t>345114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>373194</t>
+          <t>372759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758560</t>
+          <t>758419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>792152</t>
+          <t>791484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72386</t>
+          <t>69995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109004</t>
+          <t>106428</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104410</t>
+          <t>102597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144389</t>
+          <t>145880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>186355</t>
+          <t>186246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242020</t>
+          <t>239951</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>557636</t>
+          <t>560212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>594254</t>
+          <t>596645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447706</t>
+          <t>446215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487685</t>
+          <t>489498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1016715</t>
+          <t>1018784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1072380</t>
+          <t>1072489</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93020</t>
+          <t>93387</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132348</t>
+          <t>134448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167985</t>
+          <t>165861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>212894</t>
+          <t>214013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269479</t>
+          <t>271991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>331166</t>
+          <t>335157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522157</t>
+          <t>520057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>561485</t>
+          <t>561118</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>479600</t>
+          <t>478481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>524509</t>
+          <t>526633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015833</t>
+          <t>1011842</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1077520</t>
+          <t>1075008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>127237</t>
+          <t>127404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172767</t>
+          <t>172993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183074</t>
+          <t>183965</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>234078</t>
+          <t>232940</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>320048</t>
+          <t>324666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386557</t>
+          <t>391216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>426502</t>
+          <t>426276</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>472032</t>
+          <t>471865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>364385</t>
+          <t>365523</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>415389</t>
+          <t>414498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>811175</t>
+          <t>806516</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>877684</t>
+          <t>873066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>176492</t>
+          <t>175790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217024</t>
+          <t>218657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>199643</t>
+          <t>198907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>244146</t>
+          <t>245478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>388408</t>
+          <t>389208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>446892</t>
+          <t>449008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,69%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204980</t>
+          <t>203347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>245512</t>
+          <t>246214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186018</t>
+          <t>184686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>230521</t>
+          <t>231257</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>405275</t>
+          <t>403159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>463759</t>
+          <t>462959</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>142974</t>
+          <t>141472</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>178761</t>
+          <t>177290</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>176902</t>
+          <t>177241</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212955</t>
+          <t>212982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>331420</t>
+          <t>330618</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>383202</t>
+          <t>381302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125011</t>
+          <t>126482</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>160798</t>
+          <t>162300</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130417</t>
+          <t>130390</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166470</t>
+          <t>166131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>263942</t>
+          <t>265842</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>315724</t>
+          <t>316526</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118648</t>
+          <t>116488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>150672</t>
+          <t>150826</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>173452</t>
+          <t>174185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>212978</t>
+          <t>213748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>303960</t>
+          <t>303092</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>354439</t>
+          <t>355646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,41%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90636</t>
+          <t>90482</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>124820</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>165196</t>
+          <t>164426</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>203989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>265043</t>
+          <t>263836</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>315522</t>
+          <t>316390</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>808044</t>
+          <t>808272</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>923851</t>
+          <t>912678</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1128096</t>
+          <t>1132348</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1245567</t>
+          <t>1251401</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1982308</t>
+          <t>1977435</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2128182</t>
+          <t>2130614</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2403683</t>
+          <t>2414856</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2519490</t>
+          <t>2519262</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2206547</t>
+          <t>2200713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2324018</t>
+          <t>2319766</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4651466</t>
+          <t>4649034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4797340</t>
+          <t>4802213</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29274</t>
+          <t>28708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53058</t>
+          <t>53678</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33689</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57774</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68963</t>
+          <t>69422</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104122</t>
+          <t>102868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355304</t>
+          <t>354684</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379088</t>
+          <t>379654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>331684</t>
+          <t>332233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>355769</t>
+          <t>355709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>693698</t>
+          <t>694952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>728857</t>
+          <t>728398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58853</t>
+          <t>59981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92518</t>
+          <t>91944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116518</t>
+          <t>116556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157299</t>
+          <t>156595</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>186073</t>
+          <t>186773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236374</t>
+          <t>238452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490192</t>
+          <t>490766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>523857</t>
+          <t>522729</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>400842</t>
+          <t>401546</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>441623</t>
+          <t>441585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>904477</t>
+          <t>902399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>954778</t>
+          <t>954078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109022</t>
+          <t>109962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>152003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>157660</t>
+          <t>157650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>202703</t>
+          <t>201756</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>282821</t>
+          <t>278774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>343880</t>
+          <t>340311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506716</t>
+          <t>506547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>549528</t>
+          <t>548588</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>448231</t>
+          <t>449178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>493274</t>
+          <t>493284</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>965603</t>
+          <t>969172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026662</t>
+          <t>1030709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,71%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176519</t>
+          <t>176472</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225541</t>
+          <t>224323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>201292</t>
+          <t>201558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252519</t>
+          <t>249131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>390572</t>
+          <t>390882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>461778</t>
+          <t>460634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>415330</t>
+          <t>416548</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>464352</t>
+          <t>464399</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387023</t>
+          <t>390411</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>438250</t>
+          <t>437984</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>818634</t>
+          <t>819778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>889840</t>
+          <t>889530</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170108</t>
+          <t>166956</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>214163</t>
+          <t>213025</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210423</t>
+          <t>209884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>259269</t>
+          <t>256099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>388954</t>
+          <t>391096</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>454671</t>
+          <t>455650</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,3%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258702</t>
+          <t>259840</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302757</t>
+          <t>305909</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>231120</t>
+          <t>234290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>279966</t>
+          <t>280505</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>508583</t>
+          <t>507604</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>574300</t>
+          <t>572158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,4%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>158834</t>
+          <t>159295</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>194411</t>
+          <t>194104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194951</t>
+          <t>193931</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>231889</t>
+          <t>232616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>366067</t>
+          <t>365606</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>418645</t>
+          <t>419814</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,43%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>131660</t>
+          <t>131967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167237</t>
+          <t>166776</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>136771</t>
+          <t>136044</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173709</t>
+          <t>174729</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>276086</t>
+          <t>274917</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>328664</t>
+          <t>329125</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,37%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>103506</t>
+          <t>101280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131465</t>
+          <t>131236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165707</t>
+          <t>163942</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209071</t>
+          <t>209458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>276737</t>
+          <t>275905</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>332782</t>
+          <t>330809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>50,98%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118626</t>
+          <t>118855</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146585</t>
+          <t>148811</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>189756</t>
+          <t>189369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>233120</t>
+          <t>234885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>316136</t>
+          <t>318109</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>372181</t>
+          <t>373013</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>878132</t>
+          <t>879891</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>981053</t>
+          <t>986707</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1148481</t>
+          <t>1163670</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1268184</t>
+          <t>1273608</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2071546</t>
+          <t>2076240</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2225499</t>
+          <t>2232777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2358467</t>
+          <t>2352813</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2461388</t>
+          <t>2459629</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2227765</t>
+          <t>2222341</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2347468</t>
+          <t>2332279</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4609970</t>
+          <t>4602692</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4763923</t>
+          <t>4759229</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>59049</t>
+          <t>65849</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39103</t>
+          <t>46422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85365</t>
+          <t>94754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>85536</t>
+          <t>99914</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67065</t>
+          <t>77501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106732</t>
+          <t>126450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>144585</t>
+          <t>165763</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114112</t>
+          <t>135536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177179</t>
+          <t>198308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>340938</t>
+          <t>341944</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>314622</t>
+          <t>313039</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>360884</t>
+          <t>361371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>227664</t>
+          <t>262598</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206468</t>
+          <t>236062</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>246135</t>
+          <t>285011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>568602</t>
+          <t>604542</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>536008</t>
+          <t>571997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>599075</t>
+          <t>634769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>82,4%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>103680</t>
+          <t>120224</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84280</t>
+          <t>97835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130946</t>
+          <t>148324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>108441</t>
+          <t>123178</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68249</t>
+          <t>103222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134268</t>
+          <t>143027</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>212121</t>
+          <t>243402</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159719</t>
+          <t>215316</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246246</t>
+          <t>276981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>319867</t>
+          <t>356666</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292601</t>
+          <t>328566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>339267</t>
+          <t>379055</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>403063</t>
+          <t>377905</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>377236</t>
+          <t>358056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>443255</t>
+          <t>397861</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>722930</t>
+          <t>734571</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>688805</t>
+          <t>700992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>775332</t>
+          <t>762657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>77,98%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>137714</t>
+          <t>161440</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116566</t>
+          <t>136906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158081</t>
+          <t>183326</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>173287</t>
+          <t>201472</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154871</t>
+          <t>180855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190245</t>
+          <t>221086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>311001</t>
+          <t>362912</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284331</t>
+          <t>334248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337630</t>
+          <t>392703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>398624</t>
+          <t>459397</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>378257</t>
+          <t>437511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>419772</t>
+          <t>483931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>367890</t>
+          <t>419318</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>350932</t>
+          <t>399704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>386306</t>
+          <t>439935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>766514</t>
+          <t>878715</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>739885</t>
+          <t>848924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>793184</t>
+          <t>907379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541177</t>
+          <t>620790</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541177</t>
+          <t>620790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541177</t>
+          <t>620790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077515</t>
+          <t>1241627</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077515</t>
+          <t>1241627</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077515</t>
+          <t>1241627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>217352</t>
+          <t>241331</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93237</t>
+          <t>215314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>313578</t>
+          <t>266496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>254987</t>
+          <t>276711</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>220505</t>
+          <t>257329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>281043</t>
+          <t>297048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>472339</t>
+          <t>518042</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292745</t>
+          <t>489177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>573570</t>
+          <t>550945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>670434</t>
+          <t>459286</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>574208</t>
+          <t>434121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>794549</t>
+          <t>485303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>456781</t>
+          <t>459062</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>430725</t>
+          <t>438725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>491263</t>
+          <t>478444</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1127215</t>
+          <t>918348</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1025984</t>
+          <t>885445</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1306809</t>
+          <t>947213</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711768</t>
+          <t>735773</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711768</t>
+          <t>735773</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711768</t>
+          <t>735773</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1599554</t>
+          <t>1436390</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1599554</t>
+          <t>1436390</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1599554</t>
+          <t>1436390</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>246941</t>
+          <t>268580</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>225386</t>
+          <t>245588</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>269493</t>
+          <t>291634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>241683</t>
+          <t>271820</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>225565</t>
+          <t>250528</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258746</t>
+          <t>292193</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>488625</t>
+          <t>540400</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>460538</t>
+          <t>509226</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>517400</t>
+          <t>570637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>314293</t>
+          <t>340766</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>291741</t>
+          <t>317712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335848</t>
+          <t>363758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>303535</t>
+          <t>335952</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>286472</t>
+          <t>315579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319653</t>
+          <t>357244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>617827</t>
+          <t>676718</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>589052</t>
+          <t>646481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>645914</t>
+          <t>707892</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545218</t>
+          <t>607772</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545218</t>
+          <t>607772</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545218</t>
+          <t>607772</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1106452</t>
+          <t>1217118</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1106452</t>
+          <t>1217118</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1106452</t>
+          <t>1217118</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>181257</t>
+          <t>197862</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>165421</t>
+          <t>179569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>197170</t>
+          <t>214987</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>191124</t>
+          <t>210440</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75158</t>
+          <t>196055</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>293742</t>
+          <t>227427</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>372382</t>
+          <t>408302</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>202107</t>
+          <t>388632</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480806</t>
+          <t>435039</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>51,45%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>186908</t>
+          <t>209218</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170995</t>
+          <t>192093</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202744</t>
+          <t>227511</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>416702</t>
+          <t>228114</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>314084</t>
+          <t>211127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>532668</t>
+          <t>242499</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>603609</t>
+          <t>437331</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>495185</t>
+          <t>410594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>773884</t>
+          <t>457001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607826</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607826</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607826</t>
+          <t>438554</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975991</t>
+          <t>845633</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975991</t>
+          <t>845633</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975991</t>
+          <t>845633</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>145668</t>
+          <t>159284</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131169</t>
+          <t>144645</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159121</t>
+          <t>173463</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>208576</t>
+          <t>229576</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>194426</t>
+          <t>214516</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223315</t>
+          <t>243778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>354244</t>
+          <t>388860</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>335508</t>
+          <t>364716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>374950</t>
+          <t>409634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>137091</t>
+          <t>150914</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123638</t>
+          <t>136735</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>151590</t>
+          <t>165553</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>216851</t>
+          <t>234624</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202112</t>
+          <t>220422</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>231001</t>
+          <t>249684</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>353942</t>
+          <t>385538</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>333236</t>
+          <t>364764</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>372678</t>
+          <t>409682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,9%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425427</t>
+          <t>464200</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425427</t>
+          <t>464200</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425427</t>
+          <t>464200</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708186</t>
+          <t>774398</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708186</t>
+          <t>774398</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708186</t>
+          <t>774398</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1091663</t>
+          <t>1214570</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>843324</t>
+          <t>1154652</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1198696</t>
+          <t>1279714</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1263634</t>
+          <t>1413111</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1005768</t>
+          <t>1363945</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1371118</t>
+          <t>1468276</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2355296</t>
+          <t>2627681</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2048831</t>
+          <t>2555255</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2530350</t>
+          <t>2717022</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2368154</t>
+          <t>2318192</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2261121</t>
+          <t>2253048</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2616493</t>
+          <t>2378110</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2392485</t>
+          <t>2317572</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2285001</t>
+          <t>2262407</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2650351</t>
+          <t>2366738</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4760640</t>
+          <t>4635764</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4585586</t>
+          <t>4546423</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5067105</t>
+          <t>4708190</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
